--- a/outputs/py_statistical_results.xlsx
+++ b/outputs/py_statistical_results.xlsx
@@ -48740,7 +48740,7 @@
         <v>-0.03846153846153846</v>
       </c>
       <c r="D2" t="n">
-        <v>5.634628324282199</v>
+        <v>5.484269347352822</v>
       </c>
       <c r="E2" t="n">
         <v>0.001</v>
@@ -48762,10 +48762,10 @@
         <v>-0.03846153846153846</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06436148997664221</v>
+        <v>-0.02067492547824849</v>
       </c>
       <c r="E3" t="n">
-        <v>0.438</v>
+        <v>0.46</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -48784,7 +48784,7 @@
         <v>-0.03846153846153846</v>
       </c>
       <c r="D4" t="n">
-        <v>0.301906506834318</v>
+        <v>0.2998471439686877</v>
       </c>
       <c r="E4" t="n">
         <v>0.352</v>
